--- a/DOKI-Recipes.xlsx
+++ b/DOKI-Recipes.xlsx
@@ -23,15 +23,15 @@
     <sheet name="Ingredients" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Gochujangh Jerky'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Karnatka Nati Jerky'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Kerala fry Jerky'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">'Masala Jerky'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">'Mughlai Jerky'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Pepper Jerky'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">'Piri Piri Masala'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Teriyaki Jerky'!$A$1:$H$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Vinegar Bath'!$A$1:$H$54</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Gochujangh Jerky'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Karnatka Nati Jerky'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Kerala fry Jerky'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">'Masala Jerky'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">'Mughlai Jerky'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'Pepper Jerky'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">'Piri Piri Masala'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Teriyaki Jerky'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Vinegar Bath'!$A$1:$H$55</definedName>
     <definedName function="false" hidden="false" name="IngredientList" vbProcedure="false">Ingredients!$A$5:$A$55</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="228">
   <si>
     <t xml:space="preserve">DOKI recipe workbook</t>
   </si>
@@ -67,6 +67,12 @@
     <t xml:space="preserve">Fixed batches (Piri Piri Masala): weights are grams per batch — one standard size, no meat. The station skips the meat step and goes straight to recipe review with exactly these weights. Row 3 says 'Fixed batch'.</t>
   </si>
   <si>
+    <t xml:space="preserve">Papain — the last step, by meat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papain is not on any recipe sheet. For the 7 jerky recipes, once every other ingredient is in, the station asks what the meat is: buffalo gets 6 g per kg of meat, chicken gets 2 g per kg of meat; anything else gets none. Change the rates in recipes.json.</t>
+  </si>
+  <si>
     <t xml:space="preserve">What the colours mean</t>
   </si>
   <si>
@@ -85,7 +91,7 @@
     <t xml:space="preserve">Which scale gets what</t>
   </si>
   <si>
-    <t xml:space="preserve">The floor scale reads in 1 g steps. Two of those have to fit inside the tolerance before it is enforcing anything, so it only handles targets of 100 g and up — 2 × 1 g ÷ 2%. Everything smaller goes on the bench scale.</t>
+    <t xml:space="preserve">Everything from 4 g up is weighed on the main scale, where the Pi measures and logs it; only smaller items go on the small scale. The main scale reads in 1 g steps, so below 100 g it cannot hold the recipe's 2% and holds ±2 g instead — 60 g is ±2 g (3.3%), 10 g is ±2 g (20%). Those rows are amber. The 4 g setting is in recipes.json.</t>
   </si>
   <si>
     <t xml:space="preserve">The Settings sheet mirrors recipes.json, which is what the station reads. To change a scale or the tolerance, change recipes.json and rebuild this workbook — changing Settings alone changes only the workbook.</t>
@@ -118,7 +124,7 @@
     <t xml:space="preserve">MAIN SCALE — name</t>
   </si>
   <si>
-    <t xml:space="preserve">Floor scale</t>
+    <t xml:space="preserve">Main scale</t>
   </si>
   <si>
     <t xml:space="preserve">  division (g)</t>
@@ -139,7 +145,7 @@
     <t xml:space="preserve">SMALL SCALE — name</t>
   </si>
   <si>
-    <t xml:space="preserve">Bench scale</t>
+    <t xml:space="preserve">Small scale</t>
   </si>
   <si>
     <t xml:space="preserve">SPEC NOT CONFIRMED — check the label on the scale.</t>
@@ -160,7 +166,7 @@
     <t xml:space="preserve">Crossover — override</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional. Leave blank to use the derived value. A lower number keeps more ingredients on the floor scale — easier to pour into, looser tolerance, and the recipe sheets say which.</t>
+    <t xml:space="preserve">Optional. Leave blank to use the derived value. A lower number keeps more ingredients on the main scale — easier to pour into, looser tolerance, and the recipe sheets say which.</t>
   </si>
   <si>
     <t xml:space="preserve">Crossover in force (g)</t>
@@ -241,9 +247,6 @@
     <t xml:space="preserve">White vinegar</t>
   </si>
   <si>
-    <t xml:space="preserve">Papain</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t xml:space="preserve">liquid smoke</t>
   </si>
   <si>
+    <t xml:space="preserve">Last step — Papain: the station asks which meat at the end of the batch. buffalo 6 g per kg of meat, chicken 2 g per kg of meat; anything else, none. Not typed here — set in recipes.json.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gochujangh Jerky</t>
   </si>
   <si>
@@ -571,10 +577,10 @@
     <t xml:space="preserve">Measured against</t>
   </si>
   <si>
-    <t xml:space="preserve">On floor scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On bench scale</t>
+    <t xml:space="preserve">On main scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On small scale</t>
   </si>
   <si>
     <t xml:space="preserve">Cannot be weighed</t>
@@ -897,7 +903,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1020,6 +1026,10 @@
     </xf>
     <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1328,7 +1338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -1429,29 +1439,19 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1459,15 +1459,25 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -1479,25 +1489,25 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -1529,8 +1539,28 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="21">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:F4"/>
@@ -1540,16 +1570,18 @@
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1566,7 +1598,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1581,7 +1613,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1593,7 +1625,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1605,14 +1637,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -1621,14 +1653,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1637,30 +1669,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -1669,14 +1701,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1685,28 +1717,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1715,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>4.277</v>
@@ -1730,15 +1762,15 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
-        <v>0.273728</v>
+        <v>2</v>
       </c>
       <c r="H9" s="27" t="str">
         <f aca="false">IF($B9="","",IF(LEFT($F9,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F9,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G9&gt;Settings!$B$4*$E9+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1747,7 +1779,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>3.996</v>
@@ -1762,15 +1794,15 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
-        <v>0.255744</v>
+        <v>2</v>
       </c>
       <c r="H10" s="27" t="str">
         <f aca="false">IF($B10="","",IF(LEFT($F10,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F10,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G10&gt;Settings!$B$4*$E10+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1779,7 +1811,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>2.535</v>
@@ -1794,11 +1826,11 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H11" s="27" t="str">
         <f aca="false">IF($B11="","",IF(LEFT($F11,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F11,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G11&gt;Settings!$B$4*$E11+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -1811,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>43.612</v>
@@ -1826,7 +1858,7 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
@@ -1843,7 +1875,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>80.743</v>
@@ -1858,7 +1890,7 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
@@ -1875,7 +1907,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>42.055</v>
@@ -1890,7 +1922,7 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
@@ -1907,7 +1939,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>45.755</v>
@@ -1922,7 +1954,7 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
@@ -1939,7 +1971,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>78.251</v>
@@ -1954,7 +1986,7 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
@@ -1971,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>0.6</v>
@@ -1986,7 +2018,7 @@
       </c>
       <c r="F17" s="26" t="str">
         <f aca="false">IF($B17="","",IF($C17=0,"Listed — not weighed",IF($E17&lt;0,"NEITHER — negative weight",IF($E17&gt;=Settings!$B$19,Settings!$B$6,IF($E17&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E17&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF($B17="","",IF($F17=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E17),IF($F17=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E17),"")))</f>
@@ -2003,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>2</v>
@@ -2018,11 +2050,11 @@
       </c>
       <c r="F18" s="26" t="str">
         <f aca="false">IF($B18="","",IF($C18=0,"Listed — not weighed",IF($E18&lt;0,"NEITHER — negative weight",IF($E18&gt;=Settings!$B$19,Settings!$B$6,IF($E18&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E18&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF($B18="","",IF($F18=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E18),IF($F18=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E18),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H18" s="27" t="str">
         <f aca="false">IF($B18="","",IF(LEFT($F18,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F18,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G18&gt;Settings!$B$4*$E18+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -2035,7 +2067,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>1</v>
@@ -2050,7 +2082,7 @@
       </c>
       <c r="F19" s="26" t="str">
         <f aca="false">IF($B19="","",IF($C19=0,"Listed — not weighed",IF($E19&lt;0,"NEITHER — negative weight",IF($E19&gt;=Settings!$B$19,Settings!$B$6,IF($E19&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E19&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF($B19="","",IF($F19=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E19),IF($F19=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E19),"")))</f>
@@ -2067,7 +2099,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>4.55</v>
@@ -2082,15 +2114,15 @@
       </c>
       <c r="F20" s="26" t="str">
         <f aca="false">IF($B20="","",IF($C20=0,"Listed — not weighed",IF($E20&lt;0,"NEITHER — negative weight",IF($E20&gt;=Settings!$B$19,Settings!$B$6,IF($E20&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E20&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">IF($B20="","",IF($F20=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E20),IF($F20=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E20),"")))</f>
-        <v>0.2912</v>
+        <v>2</v>
       </c>
       <c r="H20" s="27" t="str">
         <f aca="false">IF($B20="","",IF(LEFT($F20,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F20,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G20&gt;Settings!$B$4*$E20+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2099,7 +2131,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>2.16</v>
@@ -2114,11 +2146,11 @@
       </c>
       <c r="F21" s="26" t="str">
         <f aca="false">IF($B21="","",IF($C21=0,"Listed — not weighed",IF($E21&lt;0,"NEITHER — negative weight",IF($E21&gt;=Settings!$B$19,Settings!$B$6,IF($E21&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E21&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF($B21="","",IF($F21=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E21),IF($F21=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E21),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H21" s="27" t="str">
         <f aca="false">IF($B21="","",IF(LEFT($F21,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F21,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G21&gt;Settings!$B$4*$E21+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -2131,7 +2163,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>2.3</v>
@@ -2146,11 +2178,11 @@
       </c>
       <c r="F22" s="26" t="str">
         <f aca="false">IF($B22="","",IF($C22=0,"Listed — not weighed",IF($E22&lt;0,"NEITHER — negative weight",IF($E22&gt;=Settings!$B$19,Settings!$B$6,IF($E22&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E22&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">IF($B22="","",IF($F22=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E22),IF($F22=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E22),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H22" s="27" t="str">
         <f aca="false">IF($B22="","",IF(LEFT($F22,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F22,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G22&gt;Settings!$B$4*$E22+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -2163,7 +2195,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>1.32</v>
@@ -2178,11 +2210,11 @@
       </c>
       <c r="F23" s="26" t="str">
         <f aca="false">IF($B23="","",IF($C23=0,"Listed — not weighed",IF($E23&lt;0,"NEITHER — negative weight",IF($E23&gt;=Settings!$B$19,Settings!$B$6,IF($E23&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E23&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">IF($B23="","",IF($F23=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E23),IF($F23=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E23),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H23" s="27" t="str">
         <f aca="false">IF($B23="","",IF(LEFT($F23,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F23,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G23&gt;Settings!$B$4*$E23+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -2195,7 +2227,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>1.2</v>
@@ -2210,7 +2242,7 @@
       </c>
       <c r="F24" s="26" t="str">
         <f aca="false">IF($B24="","",IF($C24=0,"Listed — not weighed",IF($E24&lt;0,"NEITHER — negative weight",IF($E24&gt;=Settings!$B$19,Settings!$B$6,IF($E24&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E24&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G24" s="25" t="n">
         <f aca="false">IF($B24="","",IF($F24=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E24),IF($F24=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E24),"")))</f>
@@ -2227,7 +2259,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>14</v>
@@ -2242,15 +2274,15 @@
       </c>
       <c r="F25" s="26" t="str">
         <f aca="false">IF($B25="","",IF($C25=0,"Listed — not weighed",IF($E25&lt;0,"NEITHER — negative weight",IF($E25&gt;=Settings!$B$19,Settings!$B$6,IF($E25&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E25&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G25" s="25" t="n">
         <f aca="false">IF($B25="","",IF($F25=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E25),IF($F25=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E25),"")))</f>
-        <v>0.896</v>
+        <v>2</v>
       </c>
       <c r="H25" s="27" t="str">
         <f aca="false">IF($B25="","",IF(LEFT($F25,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F25,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G25&gt;Settings!$B$4*$E25+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2259,7 +2291,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>20</v>
@@ -2274,15 +2306,15 @@
       </c>
       <c r="F26" s="26" t="str">
         <f aca="false">IF($B26="","",IF($C26=0,"Listed — not weighed",IF($E26&lt;0,"NEITHER — negative weight",IF($E26&gt;=Settings!$B$19,Settings!$B$6,IF($E26&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E26&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G26" s="25" t="n">
         <f aca="false">IF($B26="","",IF($F26=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E26),IF($F26=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E26),"")))</f>
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="H26" s="27" t="str">
         <f aca="false">IF($B26="","",IF(LEFT($F26,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F26,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G26&gt;Settings!$B$4*$E26+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2291,7 +2323,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>66.5</v>
@@ -2306,7 +2338,7 @@
       </c>
       <c r="F27" s="26" t="str">
         <f aca="false">IF($B27="","",IF($C27=0,"Listed — not weighed",IF($E27&lt;0,"NEITHER — negative weight",IF($E27&gt;=Settings!$B$19,Settings!$B$6,IF($E27&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E27&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G27" s="25" t="n">
         <f aca="false">IF($B27="","",IF($F27=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E27),IF($F27=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E27),"")))</f>
@@ -2907,7 +2939,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -2924,7 +2956,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
@@ -2943,8 +2975,19 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -2960,6 +3003,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="B53:H53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -3010,7 +3054,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3022,7 +3066,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3034,14 +3078,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3050,15 +3094,15 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B4" s="16"/>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="32" t="n">
         <f aca="false">C50</f>
         <v>2004</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3067,46 +3111,46 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
-      <c r="F5" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
+      <c r="F5" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="26"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -3115,28 +3159,28 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3145,7 +3189,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>300</v>
@@ -3160,7 +3204,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
@@ -3177,7 +3221,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>466</v>
@@ -3192,7 +3236,7 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
@@ -3209,7 +3253,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>350</v>
@@ -3224,7 +3268,7 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
@@ -3241,7 +3285,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>164</v>
@@ -3256,7 +3300,7 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
@@ -3273,7 +3317,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>164</v>
@@ -3288,7 +3332,7 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
@@ -3305,7 +3349,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>116</v>
@@ -3320,7 +3364,7 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
@@ -3337,7 +3381,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>116</v>
@@ -3352,7 +3396,7 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
@@ -3369,7 +3413,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>116</v>
@@ -3384,7 +3428,7 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
@@ -3401,7 +3445,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>60</v>
@@ -3416,15 +3460,15 @@
       </c>
       <c r="F17" s="26" t="str">
         <f aca="false">IF($B17="","",IF($C17=0,"Listed — not weighed",IF($E17&lt;0,"NEITHER — negative weight",IF($E17&gt;=Settings!$B$19,Settings!$B$6,IF($E17&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E17&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF($B17="","",IF($F17=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E17),IF($F17=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E17),"")))</f>
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H17" s="27" t="str">
         <f aca="false">IF($B17="","",IF(LEFT($F17,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F17,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G17&gt;Settings!$B$4*$E17+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3433,7 +3477,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>152</v>
@@ -3448,7 +3492,7 @@
       </c>
       <c r="F18" s="26" t="str">
         <f aca="false">IF($B18="","",IF($C18=0,"Listed — not weighed",IF($E18&lt;0,"NEITHER — negative weight",IF($E18&gt;=Settings!$B$19,Settings!$B$6,IF($E18&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E18&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF($B18="","",IF($F18=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E18),IF($F18=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E18),"")))</f>
@@ -4301,7 +4345,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -4318,7 +4362,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">E50</f>
@@ -4402,7 +4446,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4414,7 +4458,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4426,33 +4470,33 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" s="26" t="str">
         <f aca="false">'Vinegar Bath'!$C$3</f>
@@ -4460,22 +4504,22 @@
       </c>
       <c r="C5" s="26" t="n">
         <f aca="false">COUNTA('Vinegar Bath'!$B$9:$B$48)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="25" t="n">
         <f aca="false">'Vinegar Bath'!$C$50</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F5" s="26" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="26" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="26" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$F$9:$F$48,"NEITHER*")</f>
@@ -4484,7 +4528,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="26" t="str">
         <f aca="false">'Teriyaki Jerky'!$C$3</f>
@@ -4499,15 +4543,15 @@
         <v>255.05</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F6" s="26" t="n">
         <f aca="false">COUNTIF('Teriyaki Jerky'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G6" s="26" t="n">
         <f aca="false">COUNTIF('Teriyaki Jerky'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H6" s="26" t="n">
         <f aca="false">COUNTIF('Teriyaki Jerky'!$F$9:$F$48,"NEITHER*")</f>
@@ -4516,7 +4560,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="26" t="str">
         <f aca="false">'Gochujangh Jerky'!$C$3</f>
@@ -4531,15 +4575,15 @@
         <v>316.3</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F7" s="26" t="n">
         <f aca="false">COUNTIF('Gochujangh Jerky'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G7" s="26" t="n">
         <f aca="false">COUNTIF('Gochujangh Jerky'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7" s="26" t="n">
         <f aca="false">COUNTIF('Gochujangh Jerky'!$F$9:$F$48,"NEITHER*")</f>
@@ -4548,7 +4592,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B8" s="26" t="str">
         <f aca="false">'Pepper Jerky'!$C$3</f>
@@ -4563,15 +4607,15 @@
         <v>233.259</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F8" s="26" t="n">
         <f aca="false">COUNTIF('Pepper Jerky'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G8" s="26" t="n">
         <f aca="false">COUNTIF('Pepper Jerky'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8" s="26" t="n">
         <f aca="false">COUNTIF('Pepper Jerky'!$F$9:$F$48,"NEITHER*")</f>
@@ -4580,7 +4624,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="26" t="str">
         <f aca="false">'Karnatka Nati Jerky'!$C$3</f>
@@ -4595,15 +4639,15 @@
         <v>583.759</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F9" s="26" t="n">
         <f aca="false">COUNTIF('Karnatka Nati Jerky'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G9" s="26" t="n">
         <f aca="false">COUNTIF('Karnatka Nati Jerky'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H9" s="26" t="n">
         <f aca="false">COUNTIF('Karnatka Nati Jerky'!$F$9:$F$48,"NEITHER*")</f>
@@ -4612,7 +4656,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B10" s="26" t="str">
         <f aca="false">'Kerala fry Jerky'!$C$3</f>
@@ -4627,15 +4671,15 @@
         <v>466.981</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F10" s="26" t="n">
         <f aca="false">COUNTIF('Kerala fry Jerky'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G10" s="26" t="n">
         <f aca="false">COUNTIF('Kerala fry Jerky'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H10" s="26" t="n">
         <f aca="false">COUNTIF('Kerala fry Jerky'!$F$9:$F$48,"NEITHER*")</f>
@@ -4644,7 +4688,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B11" s="26" t="str">
         <f aca="false">'Mughlai Jerky'!$C$3</f>
@@ -4659,15 +4703,15 @@
         <v>338.1</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F11" s="26" t="n">
         <f aca="false">COUNTIF('Mughlai Jerky'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G11" s="26" t="n">
         <f aca="false">COUNTIF('Mughlai Jerky'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H11" s="26" t="n">
         <f aca="false">COUNTIF('Mughlai Jerky'!$F$9:$F$48,"NEITHER*")</f>
@@ -4676,7 +4720,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B12" s="26" t="str">
         <f aca="false">'Masala Jerky'!$C$3</f>
@@ -4691,15 +4735,15 @@
         <v>416.854</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F12" s="26" t="n">
         <f aca="false">COUNTIF('Masala Jerky'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G12" s="26" t="n">
         <f aca="false">COUNTIF('Masala Jerky'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H12" s="26" t="n">
         <f aca="false">COUNTIF('Masala Jerky'!$F$9:$F$48,"NEITHER*")</f>
@@ -4708,7 +4752,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B13" s="26" t="str">
         <f aca="false">'Piri Piri Masala'!$C$3</f>
@@ -4723,15 +4767,15 @@
         <v>2004</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F13" s="26" t="n">
         <f aca="false">COUNTIF('Piri Piri Masala'!$F$9:$F$48,Settings!$B$6)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="26" t="n">
         <f aca="false">COUNTIF('Piri Piri Masala'!$F$9:$F$48,Settings!$B$11)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="26" t="n">
         <f aca="false">COUNTIF('Piri Piri Masala'!$F$9:$F$48,"NEITHER*")</f>
@@ -4767,7 +4811,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4779,7 +4823,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4790,465 +4834,465 @@
       <c r="H2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>57</v>
+      <c r="A4" s="34" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="C5" s="34" t="n">
+        <v>184</v>
+      </c>
+      <c r="C5" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A5) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A5) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A5) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A5) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A5) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A5) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A5) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A5) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A5)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="34" t="n">
+        <v>185</v>
+      </c>
+      <c r="C6" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A6) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A6) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A6) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A6) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A6) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A6) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A6) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A6) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="34" t="n">
+        <v>186</v>
+      </c>
+      <c r="C7" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A7) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A7) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A7) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A7) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A7) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A7) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A7) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A7) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A7)</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="34" t="n">
+        <v>187</v>
+      </c>
+      <c r="C8" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A8) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A8) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A8) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A8) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A8) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A8) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A8) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A8) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" s="34" t="n">
+        <v>188</v>
+      </c>
+      <c r="C9" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A9) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A9) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A9) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A9) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A9) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A9) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A9) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A9) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10" s="34" t="n">
+        <v>189</v>
+      </c>
+      <c r="C10" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A10) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A10) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A10) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A10) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A10) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A10) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A10) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A10) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A10)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="34" t="n">
+        <v>190</v>
+      </c>
+      <c r="C11" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A11) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A11) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A11) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A11) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A11) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A11) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A11) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A11) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A11)</f>
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="34" t="n">
+        <v>191</v>
+      </c>
+      <c r="C12" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A12) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A12) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A12) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A12) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A12) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A12) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A12) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A12) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="C13" s="34" t="n">
+        <v>192</v>
+      </c>
+      <c r="C13" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A13) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A13) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A13) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A13) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A13) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A13) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A13) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A13) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A13)</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" s="34" t="n">
+        <v>193</v>
+      </c>
+      <c r="C14" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A14) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A14) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A14) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A14) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A14) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A14) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A14) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A14) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C15" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="C15" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A15) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A15) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A15) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A15) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A15) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A15) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A15) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A15) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="C16" s="34" t="n">
+        <v>195</v>
+      </c>
+      <c r="C16" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A16) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A16) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A16) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A16) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A16) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A16) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A16) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A16) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="C17" s="34" t="n">
+        <v>196</v>
+      </c>
+      <c r="C17" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A17) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A17) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A17) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A17) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A17) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A17) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A17) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A17) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C18" s="34" t="n">
+        <v>197</v>
+      </c>
+      <c r="C18" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A18) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A18) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A18) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A18) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A18) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A18) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A18) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A18) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A18)</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="34" t="n">
+        <v>198</v>
+      </c>
+      <c r="C19" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A19) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A19) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A19) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A19) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A19) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A19) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A19) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A19) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="34" t="n">
+        <v>199</v>
+      </c>
+      <c r="C20" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A20) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A20) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A20) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A20) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A20) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A20) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A20) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A20) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A20)</f>
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="34" t="n">
+        <v>200</v>
+      </c>
+      <c r="C21" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A21) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A21) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A21) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A21) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A21) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A21) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A21) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A21) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A21)</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="34" t="n">
+        <v>201</v>
+      </c>
+      <c r="C22" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A22) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A22) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A22) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A22) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A22) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A22) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A22) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A22) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" s="34" t="n">
+        <v>202</v>
+      </c>
+      <c r="C23" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A23) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A23) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A23) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A23) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A23) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A23) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A23) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A23) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A23)</f>
         <v>7</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" s="34" t="n">
+        <v>203</v>
+      </c>
+      <c r="C24" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A24) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A24) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A24) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A24) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A24) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A24) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A24) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A24) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C25" s="34" t="n">
+        <v>204</v>
+      </c>
+      <c r="C25" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A25) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A25) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A25) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A25) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A25) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A25) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A25) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A25) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="C26" s="34" t="n">
+        <v>205</v>
+      </c>
+      <c r="C26" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A26) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A26) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A26) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A26) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A26) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A26) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A26) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A26) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A26)</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" s="34" t="n">
+        <v>124</v>
+      </c>
+      <c r="C27" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A27) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A27) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A27) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A27) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A27) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A27) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A27) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A27) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A27)</f>
         <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="34" t="n">
+        <v>206</v>
+      </c>
+      <c r="C28" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A28) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A28) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A28) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A28) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A28) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A28) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A28) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A28) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" s="34" t="n">
+        <v>207</v>
+      </c>
+      <c r="C29" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A29) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A29) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A29) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A29) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A29) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A29) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A29) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A29) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A29)</f>
         <v>5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="C30" s="34" t="n">
+        <v>208</v>
+      </c>
+      <c r="C30" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A30) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A30) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A30) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A30) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A30) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A30) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A30) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A30) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="C31" s="34" t="n">
+        <v>209</v>
+      </c>
+      <c r="C31" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A31) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A31) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A31) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A31) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A31) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A31) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A31) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A31) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A31)</f>
         <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="C32" s="34" t="n">
+        <v>210</v>
+      </c>
+      <c r="C32" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A32) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A32) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A32) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A32) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A32) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A32) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A32) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A32) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="34" t="n">
+        <v>211</v>
+      </c>
+      <c r="C33" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A33) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A33) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A33) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A33) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A33) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A33) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A33) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A33) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="C34" s="34" t="n">
+        <v>212</v>
+      </c>
+      <c r="C34" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A34) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A34) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A34) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A34) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A34) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A34) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A34) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A34) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="34" t="n">
+        <v>213</v>
+      </c>
+      <c r="C35" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A35) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A35) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A35) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A35) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A35) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A35) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A35) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A35) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="34" t="n">
+        <v>81</v>
+      </c>
+      <c r="C36" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A36) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A36) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A36) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A36) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A36) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A36) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A36) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A36) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A36)</f>
         <v>7</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="C37" s="34" t="n">
+        <v>214</v>
+      </c>
+      <c r="C37" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A37) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A37) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A37) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A37) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A37) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A37) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A37) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A37) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A37)</f>
         <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="C38" s="34" t="n">
+        <v>215</v>
+      </c>
+      <c r="C38" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A38) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A38) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A38) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A38) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A38) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A38) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A38) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A38) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="C39" s="34" t="n">
+        <v>216</v>
+      </c>
+      <c r="C39" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A39) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A39) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A39) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A39) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A39) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A39) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A39) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A39) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A39)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="C40" s="34" t="n">
+        <v>217</v>
+      </c>
+      <c r="C40" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A40) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A40) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A40) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A40) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A40) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A40) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A40) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A40) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="34" t="n">
+        <v>125</v>
+      </c>
+      <c r="C41" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A41) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A41) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A41) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A41) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A41) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A41) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A41) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A41) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A41)</f>
         <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="C42" s="34" t="n">
+        <v>218</v>
+      </c>
+      <c r="C42" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A42) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A42) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A42) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A42) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A42) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A42) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A42) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A42) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A42)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C43" s="34" t="n">
+        <v>219</v>
+      </c>
+      <c r="C43" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A43) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A43) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A43) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A43) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A43) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A43) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A43) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A43) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A43)</f>
         <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="C44" s="34" t="n">
+        <v>220</v>
+      </c>
+      <c r="C44" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A44) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A44) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A44) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A44) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A44) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A44) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A44) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A44) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="C45" s="34" t="n">
+        <v>221</v>
+      </c>
+      <c r="C45" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A45) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A45) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A45) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A45) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A45) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A45) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A45) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A45) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A45)</f>
         <v>3</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="C46" s="34" t="n">
+        <v>222</v>
+      </c>
+      <c r="C46" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A46) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A46) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A46) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A46) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A46) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A46) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A46) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A46) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A46)</f>
         <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="C47" s="34" t="n">
+        <v>223</v>
+      </c>
+      <c r="C47" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A47) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A47) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A47) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A47) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A47) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A47) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A47) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A47) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A47)</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="34" t="n">
+        <v>74</v>
+      </c>
+      <c r="C48" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A48) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A48) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A48) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A48) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A48) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A48) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A48) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A48) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A48)</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="C49" s="34" t="n">
+        <v>224</v>
+      </c>
+      <c r="C49" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A49) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A49) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A49) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A49) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A49) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A49) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A49) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A49) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A49)</f>
         <v>2</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="C50" s="34" t="n">
+        <v>225</v>
+      </c>
+      <c r="C50" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A50) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A50) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A50) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A50) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A50) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A50) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A50) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A50) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" s="34" t="n">
+        <v>91</v>
+      </c>
+      <c r="C51" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A51) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A51) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A51) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A51) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A51) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A51) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A51) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A51) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A51)</f>
         <v>4</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="C52" s="34" t="n">
+        <v>226</v>
+      </c>
+      <c r="C52" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A52) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A52) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A52) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A52) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A52) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A52) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A52) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A52) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A52)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C53" s="34" t="n">
+        <v>227</v>
+      </c>
+      <c r="C53" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A53) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A53) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A53) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A53) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A53) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A53) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A53) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A53) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A53)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C54" s="34" t="n">
+        <v>66</v>
+      </c>
+      <c r="C54" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A54) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A54) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A54) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A54) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A54) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A54) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A54) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A54) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A54)</f>
         <v>3</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C55" s="34" t="n">
+        <v>79</v>
+      </c>
+      <c r="C55" s="35" t="n">
         <f aca="false">COUNTIF('Vinegar Bath'!$B$9:$B$48,$A55) + COUNTIF('Teriyaki Jerky'!$B$9:$B$48,$A55) + COUNTIF('Gochujangh Jerky'!$B$9:$B$48,$A55) + COUNTIF('Pepper Jerky'!$B$9:$B$48,$A55) + COUNTIF('Karnatka Nati Jerky'!$B$9:$B$48,$A55) + COUNTIF('Kerala fry Jerky'!$B$9:$B$48,$A55) + COUNTIF('Mughlai Jerky'!$B$9:$B$48,$A55) + COUNTIF('Masala Jerky'!$B$9:$B$48,$A55) + COUNTIF('Piri Piri Masala'!$B$9:$B$48,$A55)</f>
         <v>8</v>
       </c>
@@ -5283,7 +5327,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5295,7 +5339,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5307,37 +5351,37 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>50000</v>
@@ -5345,89 +5389,91 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>50000</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>3000</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>2000</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="13" t="n">
         <f aca="false">2*Settings!$B$7/Settings!$B$4</f>
         <v>100</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="C18" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B19" s="14" t="n">
         <f aca="false">IF(B18="",B17,B18)</f>
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="15" t="str">
         <f aca="false">IF(Settings!$B$14&gt;=Settings!$B$19,"None — the two scales meet","WARNING: nothing can weigh "&amp;TEXT(Settings!$B$14,"#,##0")&amp;" to "&amp;TEXT(Settings!$B$19,"#,##0")&amp;" g")</f>
@@ -5473,7 +5519,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5485,7 +5531,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5497,14 +5543,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -5513,14 +5559,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -5529,30 +5575,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -5561,12 +5607,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8"/>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -5575,28 +5621,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5605,7 +5651,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>15</v>
@@ -5620,47 +5666,43 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="H9" s="27" t="str">
         <f aca="false">IF($B9="","",IF(LEFT($F9,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F9,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G9&gt;Settings!$B$4*$E9+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="21" t="str">
         <f aca="false">IF($B10="","",2)</f>
-        <v>2</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="24" t="n">
+        <v/>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24" t="str">
         <f aca="false">IF($B10="","",$C10/1000)</f>
-        <v>0.002</v>
-      </c>
-      <c r="E10" s="25" t="n">
+        <v/>
+      </c>
+      <c r="E10" s="25" t="str">
         <f aca="false">IF($B10="","",$D10*$C$4)</f>
-        <v>6.4</v>
+        <v/>
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
-      </c>
-      <c r="G10" s="25" t="n">
+        <v/>
+      </c>
+      <c r="G10" s="25" t="str">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
-        <v>0.2</v>
+        <v/>
       </c>
       <c r="H10" s="27" t="str">
         <f aca="false">IF($B10="","",IF(LEFT($F10,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F10,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G10&gt;Settings!$B$4*$E10+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v>Held to the scale's resolution, not 2%</v>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6729,28 +6771,28 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D50" s="29" t="n">
         <f aca="false">SUM(D9:D48)</f>
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="E50" s="28" t="n">
         <f aca="false">SUM(E9:E48)</f>
-        <v>54.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
-        <v>3254.4</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6817,7 +6859,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6832,7 +6874,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6844,7 +6886,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6856,14 +6898,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -6872,14 +6914,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -6888,30 +6930,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -6920,12 +6962,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8"/>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -6934,28 +6976,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6964,7 +7006,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>73</v>
@@ -6979,7 +7021,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
@@ -6996,7 +7038,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>46.4</v>
@@ -7011,7 +7053,7 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
@@ -7028,7 +7070,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>42</v>
@@ -7043,7 +7085,7 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
@@ -7060,7 +7102,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>25.4</v>
@@ -7075,15 +7117,15 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
-        <v>1.6256</v>
+        <v>2</v>
       </c>
       <c r="H12" s="27" t="str">
         <f aca="false">IF($B12="","",IF(LEFT($F12,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F12,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G12&gt;Settings!$B$4*$E12+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7092,7 +7134,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>25.4</v>
@@ -7107,15 +7149,15 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
-        <v>1.6256</v>
+        <v>2</v>
       </c>
       <c r="H13" s="27" t="str">
         <f aca="false">IF($B13="","",IF(LEFT($F13,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F13,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G13&gt;Settings!$B$4*$E13+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7124,7 +7166,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>2</v>
@@ -7139,11 +7181,11 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H14" s="27" t="str">
         <f aca="false">IF($B14="","",IF(LEFT($F14,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F14,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G14&gt;Settings!$B$4*$E14+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -7156,7 +7198,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>23.2</v>
@@ -7171,15 +7213,15 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
-        <v>1.4848</v>
+        <v>2</v>
       </c>
       <c r="H15" s="27" t="str">
         <f aca="false">IF($B15="","",IF(LEFT($F15,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F15,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G15&gt;Settings!$B$4*$E15+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7188,7 +7230,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>7.5</v>
@@ -7203,15 +7245,15 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
-        <v>0.48</v>
+        <v>2</v>
       </c>
       <c r="H16" s="27" t="str">
         <f aca="false">IF($B16="","",IF(LEFT($F16,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F16,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G16&gt;Settings!$B$4*$E16+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7220,7 +7262,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>4.5</v>
@@ -7235,15 +7277,15 @@
       </c>
       <c r="F17" s="26" t="str">
         <f aca="false">IF($B17="","",IF($C17=0,"Listed — not weighed",IF($E17&lt;0,"NEITHER — negative weight",IF($E17&gt;=Settings!$B$19,Settings!$B$6,IF($E17&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E17&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF($B17="","",IF($F17=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E17),IF($F17=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E17),"")))</f>
-        <v>0.288</v>
+        <v>2</v>
       </c>
       <c r="H17" s="27" t="str">
         <f aca="false">IF($B17="","",IF(LEFT($F17,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F17,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G17&gt;Settings!$B$4*$E17+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7252,7 +7294,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>1</v>
@@ -7267,7 +7309,7 @@
       </c>
       <c r="F18" s="26" t="str">
         <f aca="false">IF($B18="","",IF($C18=0,"Listed — not weighed",IF($E18&lt;0,"NEITHER — negative weight",IF($E18&gt;=Settings!$B$19,Settings!$B$6,IF($E18&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E18&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF($B18="","",IF($F18=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E18),IF($F18=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E18),"")))</f>
@@ -7284,7 +7326,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>1.1</v>
@@ -7299,7 +7341,7 @@
       </c>
       <c r="F19" s="26" t="str">
         <f aca="false">IF($B19="","",IF($C19=0,"Listed — not weighed",IF($E19&lt;0,"NEITHER — negative weight",IF($E19&gt;=Settings!$B$19,Settings!$B$6,IF($E19&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E19&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF($B19="","",IF($F19=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E19),IF($F19=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E19),"")))</f>
@@ -7316,7 +7358,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>1.4</v>
@@ -7331,11 +7373,11 @@
       </c>
       <c r="F20" s="26" t="str">
         <f aca="false">IF($B20="","",IF($C20=0,"Listed — not weighed",IF($E20&lt;0,"NEITHER — negative weight",IF($E20&gt;=Settings!$B$19,Settings!$B$6,IF($E20&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E20&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">IF($B20="","",IF($F20=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E20),IF($F20=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E20),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H20" s="27" t="str">
         <f aca="false">IF($B20="","",IF(LEFT($F20,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F20,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G20&gt;Settings!$B$4*$E20+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -7348,7 +7390,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>1.3</v>
@@ -7363,11 +7405,11 @@
       </c>
       <c r="F21" s="26" t="str">
         <f aca="false">IF($B21="","",IF($C21=0,"Listed — not weighed",IF($E21&lt;0,"NEITHER — negative weight",IF($E21&gt;=Settings!$B$19,Settings!$B$6,IF($E21&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E21&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF($B21="","",IF($F21=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E21),IF($F21=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E21),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H21" s="27" t="str">
         <f aca="false">IF($B21="","",IF(LEFT($F21,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F21,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G21&gt;Settings!$B$4*$E21+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -7380,7 +7422,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>0.6</v>
@@ -7395,7 +7437,7 @@
       </c>
       <c r="F22" s="26" t="str">
         <f aca="false">IF($B22="","",IF($C22=0,"Listed — not weighed",IF($E22&lt;0,"NEITHER — negative weight",IF($E22&gt;=Settings!$B$19,Settings!$B$6,IF($E22&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E22&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">IF($B22="","",IF($F22=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E22),IF($F22=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E22),"")))</f>
@@ -7412,7 +7454,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>0.25</v>
@@ -7427,7 +7469,7 @@
       </c>
       <c r="F23" s="26" t="str">
         <f aca="false">IF($B23="","",IF($C23=0,"Listed — not weighed",IF($E23&lt;0,"NEITHER — negative weight",IF($E23&gt;=Settings!$B$19,Settings!$B$6,IF($E23&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E23&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">IF($B23="","",IF($F23=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E23),IF($F23=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E23),"")))</f>
@@ -7444,7 +7486,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>0</v>
@@ -8144,7 +8186,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -8161,7 +8203,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
@@ -8180,8 +8222,19 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -8197,6 +8250,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="B53:H53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -8232,7 +8286,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -8247,7 +8301,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8259,7 +8313,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8271,14 +8325,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -8287,14 +8341,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -8303,30 +8357,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -8335,12 +8389,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8"/>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -8349,28 +8403,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8379,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>127.5</v>
@@ -8394,7 +8448,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
@@ -8411,7 +8465,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>100</v>
@@ -8426,7 +8480,7 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
@@ -8443,7 +8497,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>40</v>
@@ -8458,7 +8512,7 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
@@ -8475,7 +8529,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>20</v>
@@ -8490,15 +8544,15 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="H12" s="27" t="str">
         <f aca="false">IF($B12="","",IF(LEFT($F12,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F12,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G12&gt;Settings!$B$4*$E12+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8507,7 +8561,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>2</v>
@@ -8522,11 +8576,11 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H13" s="27" t="str">
         <f aca="false">IF($B13="","",IF(LEFT($F13,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F13,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G13&gt;Settings!$B$4*$E13+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -8539,7 +8593,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>8</v>
@@ -8554,15 +8608,15 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
-        <v>0.512</v>
+        <v>2</v>
       </c>
       <c r="H14" s="27" t="str">
         <f aca="false">IF($B14="","",IF(LEFT($F14,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F14,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G14&gt;Settings!$B$4*$E14+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8571,7 +8625,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>6</v>
@@ -8586,15 +8640,15 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
-        <v>0.384</v>
+        <v>2</v>
       </c>
       <c r="H15" s="27" t="str">
         <f aca="false">IF($B15="","",IF(LEFT($F15,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F15,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G15&gt;Settings!$B$4*$E15+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8603,7 +8657,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>6</v>
@@ -8618,15 +8672,15 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
-        <v>0.384</v>
+        <v>2</v>
       </c>
       <c r="H16" s="27" t="str">
         <f aca="false">IF($B16="","",IF(LEFT($F16,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F16,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G16&gt;Settings!$B$4*$E16+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8635,7 +8689,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>5</v>
@@ -8650,15 +8704,15 @@
       </c>
       <c r="F17" s="26" t="str">
         <f aca="false">IF($B17="","",IF($C17=0,"Listed — not weighed",IF($E17&lt;0,"NEITHER — negative weight",IF($E17&gt;=Settings!$B$19,Settings!$B$6,IF($E17&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E17&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF($B17="","",IF($F17=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E17),IF($F17=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E17),"")))</f>
-        <v>0.32</v>
+        <v>2</v>
       </c>
       <c r="H17" s="27" t="str">
         <f aca="false">IF($B17="","",IF(LEFT($F17,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F17,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G17&gt;Settings!$B$4*$E17+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8667,7 +8721,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>1</v>
@@ -8682,7 +8736,7 @@
       </c>
       <c r="F18" s="26" t="str">
         <f aca="false">IF($B18="","",IF($C18=0,"Listed — not weighed",IF($E18&lt;0,"NEITHER — negative weight",IF($E18&gt;=Settings!$B$19,Settings!$B$6,IF($E18&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E18&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF($B18="","",IF($F18=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E18),IF($F18=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E18),"")))</f>
@@ -8699,7 +8753,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>0.8</v>
@@ -8714,7 +8768,7 @@
       </c>
       <c r="F19" s="26" t="str">
         <f aca="false">IF($B19="","",IF($C19=0,"Listed — not weighed",IF($E19&lt;0,"NEITHER — negative weight",IF($E19&gt;=Settings!$B$19,Settings!$B$6,IF($E19&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E19&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF($B19="","",IF($F19=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E19),IF($F19=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E19),"")))</f>
@@ -9539,7 +9593,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -9556,7 +9610,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
@@ -9575,8 +9629,19 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -9592,6 +9657,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="B53:H53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -9627,7 +9693,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -9642,7 +9708,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9654,7 +9720,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9666,14 +9732,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -9682,14 +9748,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -9698,30 +9764,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -9730,12 +9796,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8"/>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -9744,28 +9810,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9774,7 +9840,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>1.228</v>
@@ -9789,7 +9855,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
@@ -9806,7 +9872,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>2.148</v>
@@ -9821,11 +9887,11 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H10" s="27" t="str">
         <f aca="false">IF($B10="","",IF(LEFT($F10,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F10,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G10&gt;Settings!$B$4*$E10+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -9838,7 +9904,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>14.108</v>
@@ -9853,15 +9919,15 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
-        <v>0.902912</v>
+        <v>2</v>
       </c>
       <c r="H11" s="27" t="str">
         <f aca="false">IF($B11="","",IF(LEFT($F11,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F11,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G11&gt;Settings!$B$4*$E11+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9870,7 +9936,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>45.286</v>
@@ -9885,7 +9951,7 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
@@ -9902,7 +9968,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>161.344</v>
@@ -9917,7 +9983,7 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
@@ -9934,7 +10000,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>6.145</v>
@@ -9949,15 +10015,15 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
-        <v>0.39328</v>
+        <v>2</v>
       </c>
       <c r="H14" s="27" t="str">
         <f aca="false">IF($B14="","",IF(LEFT($F14,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F14,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G14&gt;Settings!$B$4*$E14+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9966,7 +10032,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>1</v>
@@ -9981,7 +10047,7 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
@@ -9998,7 +10064,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>2</v>
@@ -10013,11 +10079,11 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H16" s="27" t="str">
         <f aca="false">IF($B16="","",IF(LEFT($F16,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F16,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G16&gt;Settings!$B$4*$E16+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -10030,7 +10096,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>0</v>
@@ -10926,7 +10992,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -10943,7 +11009,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
@@ -10962,8 +11028,19 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -10979,6 +11056,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="B53:H53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -11014,7 +11092,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -11029,7 +11107,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11041,7 +11119,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11053,14 +11131,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -11069,14 +11147,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -11085,30 +11163,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -11117,14 +11195,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -11133,28 +11211,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11163,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>180</v>
@@ -11178,7 +11256,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
@@ -11195,7 +11273,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>0.95</v>
@@ -11210,7 +11288,7 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
@@ -11227,7 +11305,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>12</v>
@@ -11242,15 +11320,15 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
-        <v>0.768</v>
+        <v>2</v>
       </c>
       <c r="H11" s="27" t="str">
         <f aca="false">IF($B11="","",IF(LEFT($F11,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F11,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G11&gt;Settings!$B$4*$E11+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11259,7 +11337,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>7.2</v>
@@ -11274,15 +11352,15 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
-        <v>0.4608</v>
+        <v>2</v>
       </c>
       <c r="H12" s="27" t="str">
         <f aca="false">IF($B12="","",IF(LEFT($F12,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F12,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G12&gt;Settings!$B$4*$E12+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11291,7 +11369,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>36</v>
@@ -11306,7 +11384,7 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
@@ -11323,7 +11401,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>12</v>
@@ -11338,15 +11416,15 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
-        <v>0.768</v>
+        <v>2</v>
       </c>
       <c r="H14" s="27" t="str">
         <f aca="false">IF($B14="","",IF(LEFT($F14,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F14,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G14&gt;Settings!$B$4*$E14+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11355,7 +11433,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>24</v>
@@ -11370,15 +11448,15 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
-        <v>1.536</v>
+        <v>2</v>
       </c>
       <c r="H15" s="27" t="str">
         <f aca="false">IF($B15="","",IF(LEFT($F15,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F15,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G15&gt;Settings!$B$4*$E15+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11387,7 +11465,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>201.9</v>
@@ -11402,7 +11480,7 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
@@ -11419,7 +11497,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>15</v>
@@ -11434,15 +11512,15 @@
       </c>
       <c r="F17" s="26" t="str">
         <f aca="false">IF($B17="","",IF($C17=0,"Listed — not weighed",IF($E17&lt;0,"NEITHER — negative weight",IF($E17&gt;=Settings!$B$19,Settings!$B$6,IF($E17&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E17&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF($B17="","",IF($F17=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E17),IF($F17=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E17),"")))</f>
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="H17" s="27" t="str">
         <f aca="false">IF($B17="","",IF(LEFT($F17,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F17,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G17&gt;Settings!$B$4*$E17+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11451,7 +11529,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>2</v>
@@ -11466,11 +11544,11 @@
       </c>
       <c r="F18" s="26" t="str">
         <f aca="false">IF($B18="","",IF($C18=0,"Listed — not weighed",IF($E18&lt;0,"NEITHER — negative weight",IF($E18&gt;=Settings!$B$19,Settings!$B$6,IF($E18&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E18&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF($B18="","",IF($F18=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E18),IF($F18=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E18),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H18" s="27" t="str">
         <f aca="false">IF($B18="","",IF(LEFT($F18,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F18,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G18&gt;Settings!$B$4*$E18+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -11483,7 +11561,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>1</v>
@@ -11498,7 +11576,7 @@
       </c>
       <c r="F19" s="26" t="str">
         <f aca="false">IF($B19="","",IF($C19=0,"Listed — not weighed",IF($E19&lt;0,"NEITHER — negative weight",IF($E19&gt;=Settings!$B$19,Settings!$B$6,IF($E19&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E19&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF($B19="","",IF($F19=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E19),IF($F19=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E19),"")))</f>
@@ -11515,7 +11593,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>45</v>
@@ -11530,7 +11608,7 @@
       </c>
       <c r="F20" s="26" t="str">
         <f aca="false">IF($B20="","",IF($C20=0,"Listed — not weighed",IF($E20&lt;0,"NEITHER — negative weight",IF($E20&gt;=Settings!$B$19,Settings!$B$6,IF($E20&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E20&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">IF($B20="","",IF($F20=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E20),IF($F20=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E20),"")))</f>
@@ -11547,7 +11625,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>38.87</v>
@@ -11562,7 +11640,7 @@
       </c>
       <c r="F21" s="26" t="str">
         <f aca="false">IF($B21="","",IF($C21=0,"Listed — not weighed",IF($E21&lt;0,"NEITHER — negative weight",IF($E21&gt;=Settings!$B$19,Settings!$B$6,IF($E21&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E21&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF($B21="","",IF($F21=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E21),IF($F21=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E21),"")))</f>
@@ -11579,7 +11657,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>6.802</v>
@@ -11594,15 +11672,15 @@
       </c>
       <c r="F22" s="26" t="str">
         <f aca="false">IF($B22="","",IF($C22=0,"Listed — not weighed",IF($E22&lt;0,"NEITHER — negative weight",IF($E22&gt;=Settings!$B$19,Settings!$B$6,IF($E22&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E22&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">IF($B22="","",IF($F22=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E22),IF($F22=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E22),"")))</f>
-        <v>0.435328</v>
+        <v>2</v>
       </c>
       <c r="H22" s="27" t="str">
         <f aca="false">IF($B22="","",IF(LEFT($F22,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F22,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G22&gt;Settings!$B$4*$E22+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11611,7 +11689,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>1.037</v>
@@ -11626,7 +11704,7 @@
       </c>
       <c r="F23" s="26" t="str">
         <f aca="false">IF($B23="","",IF($C23=0,"Listed — not weighed",IF($E23&lt;0,"NEITHER — negative weight",IF($E23&gt;=Settings!$B$19,Settings!$B$6,IF($E23&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E23&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">IF($B23="","",IF($F23=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E23),IF($F23=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E23),"")))</f>
@@ -12339,7 +12417,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -12356,7 +12434,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
@@ -12375,8 +12453,19 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -12392,6 +12481,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="B53:H53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -12427,7 +12517,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -12442,7 +12532,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12454,7 +12544,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12466,14 +12556,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -12482,14 +12572,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -12498,30 +12588,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -12530,12 +12620,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8"/>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -12544,28 +12634,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12574,7 +12664,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>150.575</v>
@@ -12589,7 +12679,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
@@ -12606,7 +12696,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>1.839</v>
@@ -12621,11 +12711,11 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H10" s="27" t="str">
         <f aca="false">IF($B10="","",IF(LEFT($F10,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F10,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G10&gt;Settings!$B$4*$E10+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -12638,7 +12728,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>5</v>
@@ -12653,15 +12743,15 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
-        <v>0.32</v>
+        <v>2</v>
       </c>
       <c r="H11" s="27" t="str">
         <f aca="false">IF($B11="","",IF(LEFT($F11,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F11,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G11&gt;Settings!$B$4*$E11+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12670,7 +12760,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>10</v>
@@ -12685,15 +12775,15 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
-        <v>0.64</v>
+        <v>2</v>
       </c>
       <c r="H12" s="27" t="str">
         <f aca="false">IF($B12="","",IF(LEFT($F12,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F12,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G12&gt;Settings!$B$4*$E12+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12702,7 +12792,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>3</v>
@@ -12717,11 +12807,11 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H13" s="27" t="str">
         <f aca="false">IF($B13="","",IF(LEFT($F13,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F13,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G13&gt;Settings!$B$4*$E13+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -12734,7 +12824,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>4.138</v>
@@ -12749,15 +12839,15 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
-        <v>0.264832</v>
+        <v>2</v>
       </c>
       <c r="H14" s="27" t="str">
         <f aca="false">IF($B14="","",IF(LEFT($F14,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F14,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G14&gt;Settings!$B$4*$E14+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12766,7 +12856,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>4.138</v>
@@ -12781,15 +12871,15 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
-        <v>0.264832</v>
+        <v>2</v>
       </c>
       <c r="H15" s="27" t="str">
         <f aca="false">IF($B15="","",IF(LEFT($F15,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F15,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G15&gt;Settings!$B$4*$E15+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12798,7 +12888,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>30</v>
@@ -12813,15 +12903,15 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="H16" s="27" t="str">
         <f aca="false">IF($B16="","",IF(LEFT($F16,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F16,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G16&gt;Settings!$B$4*$E16+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12830,7 +12920,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>10</v>
@@ -12845,15 +12935,15 @@
       </c>
       <c r="F17" s="26" t="str">
         <f aca="false">IF($B17="","",IF($C17=0,"Listed — not weighed",IF($E17&lt;0,"NEITHER — negative weight",IF($E17&gt;=Settings!$B$19,Settings!$B$6,IF($E17&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E17&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF($B17="","",IF($F17=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E17),IF($F17=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E17),"")))</f>
-        <v>0.64</v>
+        <v>2</v>
       </c>
       <c r="H17" s="27" t="str">
         <f aca="false">IF($B17="","",IF(LEFT($F17,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F17,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G17&gt;Settings!$B$4*$E17+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12862,7 +12952,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>20</v>
@@ -12877,15 +12967,15 @@
       </c>
       <c r="F18" s="26" t="str">
         <f aca="false">IF($B18="","",IF($C18=0,"Listed — not weighed",IF($E18&lt;0,"NEITHER — negative weight",IF($E18&gt;=Settings!$B$19,Settings!$B$6,IF($E18&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E18&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF($B18="","",IF($F18=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E18),IF($F18=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E18),"")))</f>
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="H18" s="27" t="str">
         <f aca="false">IF($B18="","",IF(LEFT($F18,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F18,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G18&gt;Settings!$B$4*$E18+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12894,7 +12984,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>168.582</v>
@@ -12909,7 +12999,7 @@
       </c>
       <c r="F19" s="26" t="str">
         <f aca="false">IF($B19="","",IF($C19=0,"Listed — not weighed",IF($E19&lt;0,"NEITHER — negative weight",IF($E19&gt;=Settings!$B$19,Settings!$B$6,IF($E19&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E19&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF($B19="","",IF($F19=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E19),IF($F19=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E19),"")))</f>
@@ -12926,7 +13016,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>10</v>
@@ -12941,15 +13031,15 @@
       </c>
       <c r="F20" s="26" t="str">
         <f aca="false">IF($B20="","",IF($C20=0,"Listed — not weighed",IF($E20&lt;0,"NEITHER — negative weight",IF($E20&gt;=Settings!$B$19,Settings!$B$6,IF($E20&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E20&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">IF($B20="","",IF($F20=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E20),IF($F20=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E20),"")))</f>
-        <v>0.64</v>
+        <v>2</v>
       </c>
       <c r="H20" s="27" t="str">
         <f aca="false">IF($B20="","",IF(LEFT($F20,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F20,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G20&gt;Settings!$B$4*$E20+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12958,7 +13048,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>2</v>
@@ -12973,11 +13063,11 @@
       </c>
       <c r="F21" s="26" t="str">
         <f aca="false">IF($B21="","",IF($C21=0,"Listed — not weighed",IF($E21&lt;0,"NEITHER — negative weight",IF($E21&gt;=Settings!$B$19,Settings!$B$6,IF($E21&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E21&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G21" s="25" t="n">
         <f aca="false">IF($B21="","",IF($F21=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E21),IF($F21=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E21),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H21" s="27" t="str">
         <f aca="false">IF($B21="","",IF(LEFT($F21,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F21,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G21&gt;Settings!$B$4*$E21+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -12990,7 +13080,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>1</v>
@@ -13005,7 +13095,7 @@
       </c>
       <c r="F22" s="26" t="str">
         <f aca="false">IF($B22="","",IF($C22=0,"Listed — not weighed",IF($E22&lt;0,"NEITHER — negative weight",IF($E22&gt;=Settings!$B$19,Settings!$B$6,IF($E22&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E22&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G22" s="25" t="n">
         <f aca="false">IF($B22="","",IF($F22=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E22),IF($F22=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E22),"")))</f>
@@ -13022,7 +13112,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>38.87</v>
@@ -13037,7 +13127,7 @@
       </c>
       <c r="F23" s="26" t="str">
         <f aca="false">IF($B23="","",IF($C23=0,"Listed — not weighed",IF($E23&lt;0,"NEITHER — negative weight",IF($E23&gt;=Settings!$B$19,Settings!$B$6,IF($E23&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E23&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G23" s="25" t="n">
         <f aca="false">IF($B23="","",IF($F23=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E23),IF($F23=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E23),"")))</f>
@@ -13054,7 +13144,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>6.802</v>
@@ -13069,15 +13159,15 @@
       </c>
       <c r="F24" s="26" t="str">
         <f aca="false">IF($B24="","",IF($C24=0,"Listed — not weighed",IF($E24&lt;0,"NEITHER — negative weight",IF($E24&gt;=Settings!$B$19,Settings!$B$6,IF($E24&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E24&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G24" s="25" t="n">
         <f aca="false">IF($B24="","",IF($F24=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E24),IF($F24=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E24),"")))</f>
-        <v>0.435328</v>
+        <v>2</v>
       </c>
       <c r="H24" s="27" t="str">
         <f aca="false">IF($B24="","",IF(LEFT($F24,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F24,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G24&gt;Settings!$B$4*$E24+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13086,7 +13176,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>1.037</v>
@@ -13101,7 +13191,7 @@
       </c>
       <c r="F25" s="26" t="str">
         <f aca="false">IF($B25="","",IF($C25=0,"Listed — not weighed",IF($E25&lt;0,"NEITHER — negative weight",IF($E25&gt;=Settings!$B$19,Settings!$B$6,IF($E25&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E25&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G25" s="25" t="n">
         <f aca="false">IF($B25="","",IF($F25=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E25),IF($F25=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E25),"")))</f>
@@ -13758,7 +13848,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -13775,7 +13865,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
@@ -13794,8 +13884,19 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -13811,6 +13912,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="B53:H53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -13846,7 +13948,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -13861,7 +13963,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13873,7 +13975,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13885,14 +13987,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -13901,14 +14003,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="18" t="n">
         <v>3200</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -13917,30 +14019,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="8"/>
       <c r="D6" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="19"/>
@@ -13949,12 +14051,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="8"/>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -13963,28 +14065,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13993,7 +14095,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>200</v>
@@ -14008,7 +14110,7 @@
       </c>
       <c r="F9" s="26" t="str">
         <f aca="false">IF($B9="","",IF($C9=0,"Listed — not weighed",IF($E9&lt;0,"NEITHER — negative weight",IF($E9&gt;=Settings!$B$19,Settings!$B$6,IF($E9&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E9&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">IF($B9="","",IF($F9=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E9),IF($F9=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E9),"")))</f>
@@ -14025,7 +14127,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>75</v>
@@ -14040,7 +14142,7 @@
       </c>
       <c r="F10" s="26" t="str">
         <f aca="false">IF($B10="","",IF($C10=0,"Listed — not weighed",IF($E10&lt;0,"NEITHER — negative weight",IF($E10&gt;=Settings!$B$19,Settings!$B$6,IF($E10&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E10&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Floor scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">IF($B10="","",IF($F10=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E10),IF($F10=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E10),"")))</f>
@@ -14057,7 +14159,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C11" s="23" t="n">
         <v>20</v>
@@ -14072,15 +14174,15 @@
       </c>
       <c r="F11" s="26" t="str">
         <f aca="false">IF($B11="","",IF($C11=0,"Listed — not weighed",IF($E11&lt;0,"NEITHER — negative weight",IF($E11&gt;=Settings!$B$19,Settings!$B$6,IF($E11&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E11&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">IF($B11="","",IF($F11=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E11),IF($F11=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E11),"")))</f>
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="H11" s="27" t="str">
         <f aca="false">IF($B11="","",IF(LEFT($F11,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F11,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G11&gt;Settings!$B$4*$E11+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14089,7 +14191,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>15</v>
@@ -14104,15 +14206,15 @@
       </c>
       <c r="F12" s="26" t="str">
         <f aca="false">IF($B12="","",IF($C12=0,"Listed — not weighed",IF($E12&lt;0,"NEITHER — negative weight",IF($E12&gt;=Settings!$B$19,Settings!$B$6,IF($E12&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E12&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">IF($B12="","",IF($F12=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E12),IF($F12=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E12),"")))</f>
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="H12" s="27" t="str">
         <f aca="false">IF($B12="","",IF(LEFT($F12,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F12,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G12&gt;Settings!$B$4*$E12+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14121,7 +14223,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>2</v>
@@ -14136,11 +14238,11 @@
       </c>
       <c r="F13" s="26" t="str">
         <f aca="false">IF($B13="","",IF($C13=0,"Listed — not weighed",IF($E13&lt;0,"NEITHER — negative weight",IF($E13&gt;=Settings!$B$19,Settings!$B$6,IF($E13&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E13&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">IF($B13="","",IF($F13=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E13),IF($F13=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E13),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H13" s="27" t="str">
         <f aca="false">IF($B13="","",IF(LEFT($F13,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F13,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G13&gt;Settings!$B$4*$E13+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -14153,7 +14255,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>1.6</v>
@@ -14168,11 +14270,11 @@
       </c>
       <c r="F14" s="26" t="str">
         <f aca="false">IF($B14="","",IF($C14=0,"Listed — not weighed",IF($E14&lt;0,"NEITHER — negative weight",IF($E14&gt;=Settings!$B$19,Settings!$B$6,IF($E14&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E14&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IF($B14="","",IF($F14=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E14),IF($F14=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E14),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H14" s="27" t="str">
         <f aca="false">IF($B14="","",IF(LEFT($F14,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F14,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G14&gt;Settings!$B$4*$E14+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -14185,7 +14287,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C15" s="23" t="n">
         <v>2</v>
@@ -14200,11 +14302,11 @@
       </c>
       <c r="F15" s="26" t="str">
         <f aca="false">IF($B15="","",IF($C15=0,"Listed — not weighed",IF($E15&lt;0,"NEITHER — negative weight",IF($E15&gt;=Settings!$B$19,Settings!$B$6,IF($E15&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E15&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">IF($B15="","",IF($F15=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E15),IF($F15=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E15),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H15" s="27" t="str">
         <f aca="false">IF($B15="","",IF(LEFT($F15,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F15,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G15&gt;Settings!$B$4*$E15+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -14217,7 +14319,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" s="23" t="n">
         <v>2</v>
@@ -14232,11 +14334,11 @@
       </c>
       <c r="F16" s="26" t="str">
         <f aca="false">IF($B16="","",IF($C16=0,"Listed — not weighed",IF($E16&lt;0,"NEITHER — negative weight",IF($E16&gt;=Settings!$B$19,Settings!$B$6,IF($E16&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E16&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">IF($B16="","",IF($F16=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E16),IF($F16=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E16),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H16" s="27" t="str">
         <f aca="false">IF($B16="","",IF(LEFT($F16,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F16,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G16&gt;Settings!$B$4*$E16+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -14249,7 +14351,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>15</v>
@@ -14264,15 +14366,15 @@
       </c>
       <c r="F17" s="26" t="str">
         <f aca="false">IF($B17="","",IF($C17=0,"Listed — not weighed",IF($E17&lt;0,"NEITHER — negative weight",IF($E17&gt;=Settings!$B$19,Settings!$B$6,IF($E17&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E17&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G17" s="25" t="n">
         <f aca="false">IF($B17="","",IF($F17=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E17),IF($F17=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E17),"")))</f>
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="H17" s="27" t="str">
         <f aca="false">IF($B17="","",IF(LEFT($F17,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F17,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G17&gt;Settings!$B$4*$E17+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
-        <v/>
+        <v>Held to the scale's resolution, not 2%</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14281,7 +14383,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>2.5</v>
@@ -14296,11 +14398,11 @@
       </c>
       <c r="F18" s="26" t="str">
         <f aca="false">IF($B18="","",IF($C18=0,"Listed — not weighed",IF($E18&lt;0,"NEITHER — negative weight",IF($E18&gt;=Settings!$B$19,Settings!$B$6,IF($E18&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E18&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">IF($B18="","",IF($F18=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E18),IF($F18=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E18),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H18" s="27" t="str">
         <f aca="false">IF($B18="","",IF(LEFT($F18,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F18,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G18&gt;Settings!$B$4*$E18+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -14313,7 +14415,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>1</v>
@@ -14328,7 +14430,7 @@
       </c>
       <c r="F19" s="26" t="str">
         <f aca="false">IF($B19="","",IF($C19=0,"Listed — not weighed",IF($E19&lt;0,"NEITHER — negative weight",IF($E19&gt;=Settings!$B$19,Settings!$B$6,IF($E19&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E19&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Small scale</v>
       </c>
       <c r="G19" s="25" t="n">
         <f aca="false">IF($B19="","",IF($F19=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E19),IF($F19=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E19),"")))</f>
@@ -14345,7 +14447,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>2</v>
@@ -14360,11 +14462,11 @@
       </c>
       <c r="F20" s="26" t="str">
         <f aca="false">IF($B20="","",IF($C20=0,"Listed — not weighed",IF($E20&lt;0,"NEITHER — negative weight",IF($E20&gt;=Settings!$B$19,Settings!$B$6,IF($E20&gt;Settings!$B$14,"NEITHER — over bench capacity",IF($E20&gt;=2*Settings!$B$12,Settings!$B$11,"NEITHER — under bench resolution"))))))</f>
-        <v>Bench scale</v>
+        <v>Main scale</v>
       </c>
       <c r="G20" s="25" t="n">
         <f aca="false">IF($B20="","",IF($F20=Settings!$B$6,MAX(2*Settings!$B$7,Settings!$B$4*$E20),IF($F20=Settings!$B$11,MAX(2*Settings!$B$12,Settings!$B$4*$E20),"")))</f>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H20" s="27" t="str">
         <f aca="false">IF($B20="","",IF(LEFT($F20,6)="Listed","Quantity 0: shown on the station as a reminder, not weighed. Give it a weight to weigh it.",IF(LEFT($F20,7)="NEITHER","Cannot be weighed — split it, premix it, or raise the batch size",IF($G20&gt;Settings!$B$4*$E20+0.0001,"Held to the scale's resolution, not "&amp;TEXT(Settings!$B$4,"0%"),""))))</f>
@@ -15157,7 +15259,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" s="28" t="n">
         <f aca="false">SUM(C9:C48)</f>
@@ -15174,7 +15276,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" s="30" t="n">
         <f aca="false">$C$4+E50</f>
@@ -15193,8 +15295,19 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
     </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -15210,6 +15323,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="B53:H53">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
